--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -421,19 +421,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t># PSCBOX DIAPHRAGM  --  S15 (pier segment)</t>
+          <t># PSCBOX DIAPHRAGM  --  S15 (pier segment, P1-P3)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -441,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t># source : 평창~정선 도로건설공사 (3공구) / 일반 단면 제원도 / 도면번호 8-018 / S=1:50 / 2007.12</t>
+          <t># section : 평창~정선 도로건설공사 (3공구) / 일반 단면 제원도 / 8-018 / S=1:50 / 2007.12</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -449,7 +456,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t># S15 is the pier section: Y1 = 7,800  Y2 = 800  Y3 = 7,000  AREA = 39.922 m2</t>
+          <t># opening : 주두부 구조 일반도(P1-2) / 8-020 / 단면 A-A</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -457,7 +464,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t># bottom slab thickness follows B = 0.25 + (0.55/67.250) * X  -&gt;  0.80 m at X = 67.250</t>
+          <t># S15 is the pier section: Y1 = 7,800  Y2 = 800  Y3 = 7,000  AREA = 39.922 m2</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -465,7 +472,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t># segment length 9.000 + 9.000 = 18.000 m  (enter 18000 in Segment Length)</t>
+          <t># bottom slab thickness follows B = 0.25 + (0.55/67.250) * X  -&gt;  0.80 m at X = 67.250</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -487,62 +494,58 @@
       <c r="C7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" s="2" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pier segment 9.000 + 9.000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t># cover is not given on the drawing -- page defaults kept</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t># cover is not given on the drawings -- page defaults kept</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>cover</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="11">
-      <c r="C11" s="2" t="n"/>
-    </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t># ---- overall ----</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Y1  deck top to soffit at centreline</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,15 +555,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-3</v>
+        <v>7800</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>single -3% plane across the whole deck</t>
+          <t>Y1  deck top to soffit at centreline</t>
         </is>
       </c>
     </row>
@@ -572,12 +575,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SLR</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>-3</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>single -3% plane across the whole deck</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -587,17 +595,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SLR</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>bottom face runs parallel to the deck</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -607,11 +610,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TTS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>280</v>
+        <v>-3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>bottom face runs parallel to the deck</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -622,48 +630,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>TTS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>TBS</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Y2  bottom slab at centreline</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" s="2" t="n"/>
-    </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="C20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t># ---- widths  (right side mirrors the left) ----</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WL</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>12,400 / 2</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -673,15 +676,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WTL</t>
+          <t>WL</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3500</v>
+        <v>6200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>web outer face</t>
+          <t>12,400 / 2</t>
         </is>
       </c>
     </row>
@@ -693,7 +696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>WTL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -701,7 +704,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>bottom slab half width, 7,000 / 2</t>
+          <t>web outer face</t>
         </is>
       </c>
     </row>
@@ -713,11 +716,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WCAL1</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1750</v>
+        <v>3500</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>bottom slab half width, 7,000 / 2</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -728,11 +736,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WCAL2</t>
+          <t>WCAL1</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>950</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="26">
@@ -743,43 +751,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>WCAL2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>TWEBL</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C27" s="2" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="27">
-      <c r="C27" s="2" t="n"/>
-    </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t># ---- cantilever ----</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>TCAL</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>tip</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -789,15 +792,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TCAL1</t>
+          <t>TCAL</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>root, at the web outer face</t>
+          <t>tip</t>
         </is>
       </c>
     </row>
@@ -809,38 +812,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>TCAL1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>root, at the web outer face</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>TCAL2</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C32" s="2" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="32">
-      <c r="C32" s="2" t="n"/>
-    </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="C33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t># ---- top slab haunch : 600 at the web -&gt; 280 over a 1,750 run ----</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>TTHL1</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>600</v>
-      </c>
+      <c r="C34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -850,11 +858,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TTHL2</t>
+          <t>TTHL1</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36">
@@ -865,11 +873,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WTHUL1</t>
+          <t>TTHL2</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>875</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37">
@@ -880,7 +888,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WTHUL2</t>
+          <t>WTHUL1</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -888,30 +896,30 @@
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="2" t="n"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>WTHUL2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>875</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="C39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t># ---- bottom slab haunch : 1,050 at the web -&gt; 800 over a 1,750 run ----</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>TBHL1</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>1050</v>
-      </c>
+      <c r="C40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -921,11 +929,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TBHL2</t>
+          <t>TBHL1</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>925</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="42">
@@ -936,11 +944,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WBHUL1</t>
+          <t>TBHL2</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>875</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43">
@@ -951,7 +959,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WBHUL2</t>
+          <t>WBHUL1</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -966,38 +974,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>WBHUL2</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>TBEL</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C45" s="2" t="n">
         <v>1050</v>
       </c>
     </row>
-    <row r="45">
-      <c r="C45" s="2" t="n"/>
-    </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t># ---- fillets : the drawing has square corners ----</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>R_WTL</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t># ---- fillets : the drawings have square corners ----</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1007,7 +1015,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R_WTIL</t>
+          <t>R_WTL</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -1022,7 +1030,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R_WBL</t>
+          <t>R_WTIL</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -1030,15 +1038,104 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="2" t="n"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>R_WBL</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="C51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t># ---- diaphragm opening (8-020, section A-A) ----</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t># open | cell | shape | B | H | Cttx | Ctty | Ctbx | Ctby | X | Y</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t># 4.800 (deck top to opening top) + 1.500 (H) + 1.500 (opening bottom to soffit) = 7.800</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t># Y is measured from the top of the bottom slab: 1500 - TBS 800 = 700</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F56" t="n">
+        <v>250</v>
+      </c>
+      <c r="G56" t="n">
+        <v>250</v>
+      </c>
+      <c r="H56" t="n">
+        <v>250</v>
+      </c>
+      <c r="I56" t="n">
+        <v>250</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -1058,7 +1058,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t># ---- diaphragm opening (8-020, section A-A) ----</t>
+          <t># ---- diaphragm opening (8-020, section A-A) -- one opening, 1 Cell or 2 Cell alike ----</t>
         </is>
       </c>
       <c r="C52" s="2" t="n"/>
@@ -1066,7 +1066,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t># open | cell | shape | B | H | Cttx | Ctty | Ctbx | Ctby | X | Y</t>
+          <t># open | shape | B | H | Cttx | Ctty | Ctbx | Ctby | X | Y</t>
         </is>
       </c>
       <c r="C53" s="2" t="n"/>
@@ -1093,19 +1093,19 @@
           <t>open</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
+      <c r="C56" s="2" t="n">
+        <v>1200</v>
+      </c>
       <c r="D56" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E56" t="n">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="F56" t="n">
         <v>250</v>
@@ -1117,12 +1117,9 @@
         <v>250</v>
       </c>
       <c r="I56" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
         <v>700</v>
       </c>
     </row>
